--- a/data_extactor/batch_10_fa/batch_0033_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0033_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Education Teachers, Postsecondary (مدرسان علوم تربیتی، آموزش عالی)</t>
+          <t>مدرسان علوم تربیتی، آموزش عالی (Education Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adjunct Instructor | Assistant Professor | Associate Professor | Education Instructor | Education Professor | Faculty Member | Instructor | Lecturer | Professor | Special Education Professor</t>
+          <t>مربی مدعو | استادیار | دانشیار | مدرس علوم تربیتی | استاد علوم تربیتی | عضو هیئت علمی | مدرس | مدرس | استاد | استاد آموزش استثنایی</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Blackboard software | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Desmos | Editing software | Email software | Geogebra | Google Docs | Image scanning software | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | SAS | Sakai CLE | VoiceThread | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Desmos | Editing software | نرم‌افزار ایمیل | Geogebra | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | SAS | Sakai CLE | VoiceThread | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Speaking | Reading Comprehension | Learning Strategies | Active Listening | Writing | Active Learning | Monitoring | Critical Thinking</t>
+          <t>سخن گفتن | درک مطلب | راهبردهای یادگیری | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Psychology | Sociology and Anthropology | Communications and Media | Administration and Management | Mathematics | Customer and Personal Service | Personnel and Human Resources | Computers and Electronics | Philosophy and Theology</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | مدیریت و اداره | ریاضیات | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Speech Clarity | Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Problem Sensitivity | Category Flexibility | Information Ordering | Originality | Fluency of Ideas</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail | Freedom to Make Decisions | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Contact With Others | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | Public Speaking | Frequency of Decision Making | Deal With External Customers or the Public in General | Spend Time Sitting | Impact of Decisions on Co-workers or Company Results | Level of Competition | Written Letters and Memos | Time Pressure</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | سخنرانی عمومی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Middle School | Communications Teachers, Postsecondary | Education Administrators, Postsecondary | Educational, Guidance, and Career Counselors and Advisors | Elementary School Teachers, Except Special Education | Family and Consumer Sciences Teachers, Postsecondary | Instructional Coordinators | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Psychology Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان ارتباطات، آموزش عالی | مدیران آموزشی، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise and instruct teachers employed in school systems by providing activities, such as in-service seminars. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as children's literature, learning and development, and reading instruction. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve as a liaison between the university and other governmental and educational agencies. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise students' fieldwork, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | ارائه مشاوره و آموزش به معلمان شاغل در نظام‌های آموزشی از راه برگزاری فعالیت‌هایی مانند سمینارهای ضمن خدمت. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند ادبیات کودک، یادگیری و رشد، و آموزش خواندن. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | ایفای نقش رابط میان دانشگاه و سایر نهادهای دولتی و آموزشی. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | سرپرستی کار میدانی، کارآموزی و فعالیت پژوهشی دانشجویان. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Library Science Teachers, Postsecondary (مدرسان علوم کتابداری، آموزش عالی)</t>
+          <t>مدرسان علوم کتابداری، آموزش عالی (Library Science Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Classification Instructor | Information Science Professor | Instructor | Lecturer | Library Instructor | Library Science Professor | Library Technology Instructor | Professor</t>
+          <t>استادیار | دانشیار | مدرس طبقه‌بندی | استاد علم اطلاعات | مدرس | مدرس | مدرس کتابداری | استاد علم کتابداری | مدرس فناوری کتابخانه | استاد</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon Elastic Compute Cloud EC2 | Association for Computing Machinery Digital Library | Blackboard Learn | C++ | Collaborative editing software | Course management system software | DOC Cop | Database management system software | Desire2Learn LMS software | EBSCO Information Services Academic Search Premier | EBSCO Information Services Library Literature and Information Science Index | EBSCO Library, Information Science, and Technology Abstracts LISTSA | EBSCO OmniFile FullText Mega | Elsevier ScienceDirect | Email software | Emerald Insight Emerald Management Xtra | Extensible markup language XML | Extensible stylesheet language transformations XSLT | Gale Cengage Learning Associations Unlimited | Google Docs | Hyland OnBase Enterprise Content Management | ITHAKA JSTOR | Image scanning software | JavaScript | Learning management system LMS | LexisNexis | Library of Congress online databases | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | MySQL | OCLC ILLiad | Online Dictionary for Library and Information Science ODLIS | PHP | ProQuest ABI/INFORM Global | ProQuest ERIC | ProQuest Library and Information Science Abstracts LISA | Sakai CLE | Social networking platforms | Splunk Enterprise | Structured query language SQL | Thomson Reuters Web of Science | Ulrichsweb | Web browser software | Web conferencing software | iParadigms Turnitin</t>
+          <t>Amazon Elastic Compute Cloud EC2 | Association for Computing Machinery Digital Library | Blackboard Learn | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | Database management system software | نرم‌افزار Desire2Learn LMS | EBSCO Information Services Academic Search Premier | EBSCO Information Services Library Literature and Information Science Index | EBSCO Library, Information Science, and Technology Abstracts LISTSA | EBSCO OmniFile FullText Mega | Elsevier ScienceDirect | نرم‌افزار ایمیل | Emerald Insight Emerald Management Xtra | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Gale Cengage Learning Associations Unlimited | Google Docs | Hyland OnBase Enterprise Content Management | ITHAKA JSTOR | نرم‌افزار اسکن تصویر | JavaScript | سیستم مدیریت یادگیری LMS | LexisNexis | Library of Congress online databases | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | MySQL | OCLC ILLiad | Online Dictionary for Library and Information Science ODLIS | PHP | ProQuest ABI/INFORM Global | ProQuest ERIC | ProQuest Library and Information Science Abstracts LISA | Sakai CLE | Social networking platforms | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | Thomson Reuters Web of Science | Ulrichsweb | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Speaking | Monitoring | Learning Strategies | Active Learning | Critical Thinking | Writing | Active Listening</t>
+          <t>درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Computers and Electronics | Customer and Personal Service | Communications and Media | Sociology and Anthropology | Psychology | Administration and Management</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Written Comprehension | Oral Comprehension | Oral Expression | Written Expression | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Problem Sensitivity | Category Flexibility | Information Ordering</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Time Pressure | Frequency of Decision Making</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Middle School | Communications Teachers, Postsecondary | Computer Science Teachers, Postsecondary | Education Administrators, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Instructional Coordinators | Law Teachers, Postsecondary | Librarians and Media Collections Specialists | Library Assistants, Clerical | Library Technicians | Middle School Teachers, Except Special and Career/Technical Education | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Teaching Assistants, Postsecondary | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان ارتباطات، آموزش عالی | اساتید علوم رایانه، پس از متوسطه | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان حقوق، آموزش عالی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | تکنسین‌های کتابخانه | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and present findings in professional journals, books, electronic media, or at professional conferences. | Develop and teach online courses. | Edit manuscripts for professional journals. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, giving presentations at conferences, and serving on committees in professional associations. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as collection development, archival methods, and indexing and abstracting. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and invite guest speakers to speak to classes. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها، رسانه‌های الکترونیکی یا کنفرانس‌های حرفه‌ای ارائه دهید. | تدوین و تدریس دوره‌های برخط. | ویرایش دست‌نوشته‌ها برای نشریات تخصصی. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | به‌روز ماندن از تحولات این حوزه از راه مطالعه ادبیات روز، گفت‌وگو با همکاران، ارائه در همایش‌ها و عضویت در کمیته‌های انجمن‌های تخصصی. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند توسعه مجموعه، روش‌های بایگانی، و نمایه‌سازی و چکیده‌نویسی. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | انتخاب و دعوت از سخنرانان مهمان برای حضور در کلاس‌ها. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Criminal Justice and Law Enforcement Teachers, Postsecondary (مدرسان عدالت کیفری و اجرای قانون، آموزش عالی)</t>
+          <t>مدرسان عدالت کیفری و اجرای قانون، آموزش عالی (Criminal Justice and Law Enforcement Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adjunct Instructor | Adjunct Professor | Assistant Professor | Associate Professor | Criminal Justice Instructor | Criminal Justice Professor | Digital Forensics Instructor | Instructor | Justice Professor | Professor</t>
+          <t>مربی مدعو | استاد مدعو | استادیار | دانشیار | مدرس عدالت کیفری | استاد عدالت کیفری | مدرس جرم‌شناسی دیجیتال | مدرس | استاد عدالت کیفری | استاد</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Blackboard software | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Distance learning software | Email software | Google Docs | Image scanning software | Learning management system LMS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | National Crime Information Center (NCIC) database | Sakai CLE | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Distance learning software | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Speaking | Critical Thinking | Active Listening | Writing | Reading Comprehension | Active Learning | Learning Strategies | Monitoring</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Law and Government | Public Safety and Security | Customer and Personal Service | Computers and Electronics | Administration and Management | Psychology | Administrative | Personnel and Human Resources | Communications and Media</t>
+          <t>آموزش و پرورش | زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | روان‌شناسی | اداری | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Speech Clarity | Inductive Reasoning | Deductive Reasoning | Near Vision | Problem Sensitivity | Speech Recognition | Information Ordering | Category Flexibility | Originality | Fluency of Ideas</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Telephone Conversations | Deal With External Customers or the Public in General | Public Speaking | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Importance of Being Exact or Accurate</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Business Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Communications Teachers, Postsecondary | Economics Teachers, Postsecondary | Education Administrators, Postsecondary | Education Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Instructional Coordinators | Law Teachers, Postsecondary | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Political Science Teachers, Postsecondary | Psychology Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Special Education Teachers, Secondary School</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان ارتباطات، آموزش عالی | استادان اقتصاد، پس از متوسطه | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as criminal law, defensive policing, and investigation techniques. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding. | Write letters of recommendation for students.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند حقوق کیفری، پلیس دفاعی و فنون بازپرسی. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید. | برای دانشجویان توصیه‌نامه بنویسید.</t>
         </is>
       </c>
     </row>
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Law Teachers, Postsecondary (مدرسان حقوق، آموزش عالی)</t>
+          <t>مدرسان حقوق، آموزش عالی (Law Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adjunct Professor | Assistant Professor | Associate Professor | Business Law Professor | Clinical Law Professor | Instructor | Law Instructor | Law Professor | Legal Writing Professor | Professor</t>
+          <t>استاد مدعو | استادیار | دانشیار | استاد حقوق تجارت | استاد حقوق بالینی | مدرس | مدرس حقوق | استاد حقوق | استاد نگارش حقوقی | استاد</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACD Systems Canvas | AbacusNext HotDocs | Blackboard Learn | CT Summation iBlaze | Center for Computer-Assisted Legal Instruction CALI Author | Center for Computer-Assisted Legal Instruction CALI Classcaster | Collaborative editing software | Collateral Consequences Calculator | Course management system software | DOC Cop | Desire2Learn LMS software | Email software | ExamSoft Exam Intelligence | Google Docs | Image scanning software | Learning management system LMS | LexisNexis | LexisNexis CaseMap | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Panopto | Piazza | Sakai CLE | Thomson Reuters Westlaw | Thomson Reuters WestlawNext Litigator | Web browser software | iParadigms Turnitin</t>
+          <t>ACD Systems Canvas | AbacusNext HotDocs | Blackboard Learn | CT Summation iBlaze | Center for Computer-Assisted Legal Instruction CALI Author | Center for Computer-Assisted Legal Instruction CALI Classcaster | نرم‌افزار ویرایش مشارکتی | Collateral Consequences Calculator | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | ExamSoft Exam Intelligence | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | LexisNexis | LexisNexis CaseMap | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Panopto | Piazza | Sakai CLE | Thomson Reuters Westlaw | Thomson Reuters WestlawNext Litigator | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Learning Strategies | Active Learning | Critical Thinking | Writing | Monitoring</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Law and Government | English Language | Education and Training | Computers and Electronics | Communications and Media</t>
+          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oral Expression | Written Comprehension | Oral Comprehension | Speech Clarity | Written Expression | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Problem Sensitivity | Category Flexibility | Information Ordering | Originality | Fluency of Ideas</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Determine Tasks, Priorities and Goals | E-Mail | Freedom to Make Decisions | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Public Speaking | Telephone Conversations | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Spend Time Sitting</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | ایمیل | آزادی در تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Business Teachers, Postsecondary | Communications Teachers, Postsecondary | Criminal Justice and Law Enforcement Teachers, Postsecondary | Economics Teachers, Postsecondary | Education Administrators, Postsecondary | Education Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | History Teachers, Postsecondary | Instructional Coordinators | Lawyers | Library Science Teachers, Postsecondary | Philosophy and Religion Teachers, Postsecondary | Political Science Teachers, Postsecondary | Political Scientists | Psychology Teachers, Postsecondary | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Teaching Assistants, Postsecondary</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | استادان اقتصاد، پس از متوسطه | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان تاریخ، آموزش عالی | هماهنگ‌کنندگان آموزشی | وکلا | مدرسان علوم کتابداری، آموزش عالی | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | استادان روان‌شناسی، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Assign cases for students to hear and try. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, papers, and oral presentations. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as civil procedure, contracts, and torts. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | واگذاری پرونده‌ها به دانشجویان برای استماع و رسیدگی. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | ارزیابی و نمره‌دهی به فعالیت کلاسی، تکالیف، مقالات و ارائه‌های شفاهی دانشجویان. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند آیین دادرسی مدنی، قراردادها و مسئولیت مدنی. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Social Work Teachers, Postsecondary (مدرسان مددکاری اجتماعی، آموزش عالی)</t>
+          <t>مدرسان مددکاری اجتماعی، آموزش عالی (Social Work Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adjunct Professor | Assistant Professor | Clinical Professor | Faculty Member | Field Education Coordinator | Professor | Social Work Associate Professor | Social Work Instructor | Social Work Lecturer | Social Work Professor</t>
+          <t>استاد مدعو | استادیار | استاد بالینی | عضو هیئت علمی | هماهنگ‌کننده آموزش میدانی | استاد | دانشیار مددکاری اجتماعی | مدرس مددکاری اجتماعی | مدرس مددکاری اجتماعی | استاد مددکاری اجتماعی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Blackboard Learn | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Email software | Google Docs | Image scanning software | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | Web browser software | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Speaking | Learning Strategies | Writing | Active Listening | Reading Comprehension | Active Learning | Critical Thinking | Monitoring</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Education and Training | Sociology and Anthropology | Therapy and Counseling | English Language | Psychology | Computers and Electronics | Administration and Management | Customer and Personal Service | Communications and Media | Law and Government</t>
+          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oral Expression | Speech Clarity | Oral Comprehension | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Near Vision | Problem Sensitivity | Fluency of Ideas | Information Ordering | Category Flexibility | Originality</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mail | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Telephone Conversations | Work With or Contribute to a Work Group or Team | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Sitting | Deal With External Customers or the Public in General | Public Speaking | Time Pressure | Written Letters and Memos</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | سخنرانی عمومی | فشار زمانی | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Communications Teachers, Postsecondary | Education Teachers, Postsecondary | Educational, Guidance, and Career Counselors and Advisors | Elementary School Teachers, Except Special Education | Family and Consumer Sciences Teachers, Postsecondary | Instructional Coordinators | Law Teachers, Postsecondary | Library Science Teachers, Postsecondary | Political Science Teachers, Postsecondary | Psychology Teachers, Postsecondary | Recreation and Fitness Studies Teachers, Postsecondary | School Psychologists | Secondary School Teachers, Except Special and Career/Technical Education | Sociologists | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues and community agencies to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Mentor new faculty members. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as family behavior, child and adolescent mental health, or social intervention evaluation. | Prepare course materials, such as syllabi, homework assignments, or handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks or laboratory equipment. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise students' laboratory and field work. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | همکاری با همکاران و نهادهای اجتماعی برای رسیدگی به مسائل آموزشی و پژوهشی. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | راهنمایی و پشتیبانی اعضای جدید هیئت علمی. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند رفتار خانواده، سلامت روان کودک و نوجوان، یا ارزیابی مداخله اجتماعی. | تهیه مواد درسی، مانند سرفصل‌ها، تکالیف یا جزوه‌ها. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | انتخاب و تهیه مواد و ملزومات، مانند کتاب‌های درسی یا تجهیزات آزمایشگاهی. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر کارهای آزمایشگاهی و میدانی دانشجویان نظارت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Art, Drama, and Music Teachers, Postsecondary (مدرسان هنر، نمایش و موسیقی، آموزش عالی)</t>
+          <t>مدرسان هنر، نمایش و موسیقی، آموزش عالی (Art, Drama, and Music Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Art History Professor | Art Instructor | Art Professor | Assistant Professor | Associate Professor | Instructor | Music Instructor | Music Professor | Professor | Theater Professor</t>
+          <t>استاد تاریخ هنر | مدرس هنر | استاد هنر | استادیار | دانشیار | مدرس | مدرس موسیقی | استاد موسیقی | استاد | استاد تئاتر</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe After Effects | Adobe Audition | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple DVD Studio Pro | Apple Final Cut Pro | Apple Logic Pro | Autodesk Maya | Autodesk MotionBuilder | Blackboard Learn | Blackboard software | Cascading style sheets CSS | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Edmodo | Email software | Faux Labs Splashup | Google Docs | Hypertext markup language HTML | Image scanning software | JavaScript | Komplete Kontrol | Learning management system LMS | Linux | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Studio | Microsoft Word | Moodle | MySQL | Next Limit Maxwell Render | PHP | PhoneGap | Pixar RenderMan Studio | Propellerhead Software Reason | Pure Data PD | QuarkXPress | Red Giant Trapcode Particular | Sakai CLE | Sonic Studio audio software | The Foundry Nuke | The Pixel Farm PFTrack | Web browser software | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | Adobe After Effects | Adobe Audition | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple DVD Studio Pro | Apple Final Cut Pro | Apple Logic Pro | Autodesk Maya | Autodesk MotionBuilder | Blackboard Learn | نرم‌افزار Blackboard | برگه‌های سبک آبشاری CSS | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Edmodo | نرم‌افزار ایمیل | Faux Labs Splashup | Google Docs | زبان نشانه‌گذاری ابرمتن HTML | نرم‌افزار اسکن تصویر | JavaScript | Komplete Kontrol | سیستم مدیریت یادگیری LMS | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Studio | Microsoft Word | Moodle | MySQL | Next Limit Maxwell Render | PHP | PhoneGap | Pixar RenderMan Studio | Propellerhead Software Reason | Pure Data PD | QuarkXPress | Red Giant Trapcode Particular | Sakai CLE | Sonic Studio audio software | The Foundry Nuke | The Pixel Farm PFTrack | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Speaking | Learning Strategies | Active Learning | Active Listening | Reading Comprehension | Writing | Monitoring | Critical Thinking</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fine Arts | Education and Training | English Language | Communications and Media | History and Archeology | Psychology | Philosophy and Theology | Computers and Electronics | Sociology and Anthropology</t>
+          <t>هنرهای زیبا | آموزش و پرورش | زبان انگلیسی | ارتباطات و رسانه | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oral Expression | Written Comprehension | Written Expression | Oral Comprehension | Speech Clarity | Originality | Near Vision | Speech Recognition | Inductive Reasoning | Deductive Reasoning | Fluency of Ideas | Problem Sensitivity | Far Vision | Category Flexibility | Information Ordering | Visual Color Discrimination | Visualization</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | اصالت | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | حساسیت به مسئله | بینایی دور | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail | Contact With Others | Indoors, Environmentally Controlled | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Public Speaking | Work With or Contribute to a Work Group or Team | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity</t>
+          <t>ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Architecture Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Choreographers | Communications Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | History Teachers, Postsecondary | Instructional Coordinators | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Music Directors and Composers | Philosophy and Religion Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Teaching Assistants, Postsecondary | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان معماری، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | طراحان رقص | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان تاریخ، آموزش عالی | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مدیران موسیقی و آهنگسازان | اساتید فلسفه و دین، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Display students' work in schools, galleries, and exhibitions. | Evaluate and grade students' class work, performances, projects, assignments, and papers. | Explain and demonstrate artistic techniques. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Keep students informed of community events, such as plays and concerts. | Maintain or repair studio facilities. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Organize performance groups and direct their rehearsals. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as acting techniques, fundamentals of music, and art history. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Prepare students for performances, exams, or assessments. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks and performance pieces. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | به نمایش گذاشتن آثار دانشجویان در مدارس، نگارخانه‌ها و نمایشگاه‌ها. | ارزیابی و نمره‌دهی به فعالیت کلاسی، اجراها، پروژه‌ها، تکالیف و مقالات دانشجویان. | تشریح و نمایش عملی فنون هنری. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | آگاه نگه‌داشتن دانشجویان از رویدادهای فرهنگی جامعه، مانند نمایش‌ها و کنسرت‌ها. | نگهداری یا تعمیر تجهیزات و فضای کارگاه هنری. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | سازماندهی گروه‌های اجرایی و هدایت تمرین‌های آنان. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند فنون بازیگری، مبانی موسیقی و تاریخ هنر. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | آماده‌سازی دانشجویان برای اجراها، آزمون‌ها یا ارزیابی‌ها. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | انتخاب و تهیه مواد و ملزومات، مانند کتاب‌های درسی و قطعات اجرایی. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Communications Teachers, Postsecondary (مدرسان ارتباطات، آموزش عالی)</t>
+          <t>مدرسان ارتباطات، آموزش عالی (Communications Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Communication Arts Professor | Communication Instructor | Communication Professor | Instructor | Mass Communications Professor | Professor | Speech Instructor | Speech Professor</t>
+          <t>استادیار | دانشیار | استاد هنرهای ارتباطی | مدرس ارتباطات | استاد ارتباطات | مدرس | استاد ارتباطات جمعی | استاد | مدرس فن بیان | استاد فن بیان</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Audition | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Audacity | Avid Technology Media Composer | Avid Technology Pro Tools | Blackboard Learn | Blackboard software | Collaborative editing software | Course management system software | DOC Cop | Data visualization software | Desire2Learn LMS software | Email software | Google Docs | Image scanning software | Learning management system LMS | LinkedIn | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Moodle | Sakai CLE | Video editing software | Video production software | Web browser software | WideOrbit | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | Adobe Audition | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Audacity | Avid Technology Media Composer | Avid Technology Pro Tools | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار تجسم داده | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | LinkedIn | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Moodle | Sakai CLE | نرم‌افزار ویرایش ویدیو | Video production software | نرم‌افزار مرورگر وب | WideOrbit | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Active Listening | Speaking | Writing | Learning Strategies | Active Learning | Critical Thinking | Monitoring</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Communications and Media | Psychology | Computers and Electronics | Sociology and Anthropology | Customer and Personal Service | Philosophy and Theology | Administrative | History and Archeology | Administration and Management | Fine Arts</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | فلسفه و الهیات | اداری | تاریخ و باستان‌شناسی | مدیریت و اداره | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Speech Clarity | Written Comprehension | Written Expression | Speech Recognition | Deductive Reasoning | Inductive Reasoning | Near Vision | Information Ordering | Problem Sensitivity | Selective Attention | Originality | Fluency of Ideas</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-Mail | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Contact With Others | Determine Tasks, Priorities and Goals | Public Speaking | Frequency of Decision Making | Time Pressure | Spend Time Sitting | Work With or Contribute to a Work Group or Team | Telephone Conversations | Importance of Being Exact or Accurate | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | سخنرانی عمومی | فراوانی تصمیم‌گیری | فشار زمانی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Business Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Instructional Coordinators | Law Teachers, Postsecondary | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Philosophy and Religion Teachers, Postsecondary | Political Science Teachers, Postsecondary | Psychology Teachers, Postsecondary | Public Relations Managers | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Teaching Assistants, Postsecondary</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | هماهنگ‌کنندگان آموزشی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | مدیران روابط عمومی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments and technological advances in the communication field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as public speaking, media criticism, and oral traditions. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | به‌روز ماندن از تحولات و پیشرفت‌های فناورانه حوزه ارتباطات از راه مطالعه ادبیات روز، گفت‌وگو با همکاران و شرکت در همایش‌های تخصصی. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند سخنرانی عمومی، نقد رسانه و سنت‌های شفاهی. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>English Language and Literature Teachers, Postsecondary (مدرسان زبان و ادبیات انگلیسی، آموزش عالی)</t>
+          <t>مدرسان زبان و ادبیات انگلیسی، آموزش عالی (English Language and Literature Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Creative Writing Professor | English Instructor | English Professor | Humanities Professor | Instructor | Lecturer | Literature Professor | Professor</t>
+          <t>استادیار | دانشیار | استاد نویسندگی خلاق | مدرس زبان انگلیسی | استاد زبان انگلیسی | استاد علوم انسانی | مدرس | مدرس | استاد ادبیات | استاد</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Acrobat Reader | Adobe Illustrator | Adobe Photoshop | Apple QuickTime | Apple Safari | Blackboard Collaborate | Blackboard Learn | Blackboard software | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Email software | Google Chrome | Google Docs | Graphics creation software | Image scanning software | Learning management system LMS | Lucidchart | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | VLC Media Player | Web browser software | iParadigms Turnitin</t>
+          <t>Adobe Acrobat Reader | Adobe Illustrator | Adobe Photoshop | Apple QuickTime | Apple Safari | Blackboard Collaborate | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Chrome | Google Docs | نرم‌افزار ایجاد گرافیک | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Lucidchart | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | VLC Media Player | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Writing | Speaking | Learning Strategies | Active Listening | Active Learning | Critical Thinking | Monitoring</t>
+          <t>درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Communications and Media | History and Archeology | Philosophy and Theology | Sociology and Anthropology | Customer and Personal Service | Computers and Electronics | Psychology | Administrative | Fine Arts</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | روان‌شناسی | اداری | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Written Comprehension | Oral Expression | Oral Comprehension | Written Expression | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Problem Sensitivity | Fluency of Ideas | Originality | Category Flexibility</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Environmentally Controlled | Contact With Others | Public Speaking | Face-to-Face Discussions with Individuals and Within Teams | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Sitting</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Art, Drama, and Music Teachers, Postsecondary | Communications Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | Family and Consumer Sciences Teachers, Postsecondary | Foreign Language and Literature Teachers, Postsecondary | History Teachers, Postsecondary | Instructional Coordinators | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Philosophy and Religion Teachers, Postsecondary | Psychology Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Sociology Teachers, Postsecondary | Teaching Assistants, Postsecondary | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان زبان و ادبیات خارجی، آموزش عالی | مدرسان تاریخ، آموزش عالی | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Assist students who need extra help with their coursework outside of class. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Conduct staff performance evaluations. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in cultural and literary activities, such as traveling abroad and attending performing arts events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as poetry, novel structure, and translation and adaptation. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide assistance to students in college writing centers. | Provide professional consulting services to government or industry. | Recruit, train, and supervise department personnel, such as faculty and student writing instructors. | Review manuscripts for publication in professional journals. | Schedule courses. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Teach classes using online technology. | Teach writing or communication classes. | Write grant proposals to procure external research funding. | Write letters of recommendation for students. | Write original literary pieces.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | به دانشجویانی که خارج از کلاس به کمک بیشتری در دروس خود نیاز دارند، کمک کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | انجام ارزیابی عملکرد کارکنان. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | مشارکت در فعالیت‌های فرهنگی و ادبی، مانند سفر به خارج از کشور و حضور در رویدادهای هنرهای نمایشی. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند شعر، ساختار رمان، و ترجمه و اقتباس. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | ارائه کمک به دانشجویان در مراکز نگارش دانشکده. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | جذب، آموزش و سرپرستی کارکنان گروه آموزشی، مانند اعضای هیئت علمی و مدرسان نگارش دانشجویی. | داوری دست‌نوشته‌ها برای انتشار در نشریات تخصصی. | زمان‌بندی دروس. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | تدریس کلاس‌ها با استفاده از فناوری برخط. | تدریس کلاس‌های نگارش یا ارتباطات. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید. | برای دانشجویان توصیه‌نامه بنویسید. | نگارش آثار ادبی اصیل.</t>
         </is>
       </c>
     </row>
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Foreign Language and Literature Teachers, Postsecondary (مدرسان زبان و ادبیات خارجی، آموزش عالی)</t>
+          <t>مدرسان زبان و ادبیات خارجی، آموزش عالی (Foreign Language and Literature Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Foreign Languages Professor | French Professor | German Professor | Instructor | Modern Languages Professor | Professor | Spanish Instructor | Spanish Professor</t>
+          <t>استادیار | دانشیار | استاد زبان‌های خارجی | استاد زبان فرانسه | استاد زبان آلمانی | مدرس | استاد زبان‌های مدرن | استاد | مدرس زبان اسپانیایی | استاد زبان اسپانیایی</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Illustrator | Adobe PageMaker | Adobe Photoshop | American Sign Language ASL browser | Audacity | Blackboard Learn | Blackboard software | Collaborative editing software | Computer assisted language learning CALL software | Course management system software | DOC Cop | Desire2Learn LMS software | Email software | Google Docs | Image scanning software | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | QuarkXPress | Sakai CLE | Skype | Web browser software | Zoom | iParadigms Turnitin</t>
+          <t>Adobe Illustrator | Adobe PageMaker | Adobe Photoshop | American Sign Language ASL browser | Audacity | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | Computer assisted language learning CALL software | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | QuarkXPress | Sakai CLE | Skype | نرم‌افزار مرورگر وب | Zoom | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Speaking | Writing | Active Listening | Reading Comprehension | Learning Strategies | Active Learning | Critical Thinking | Monitoring</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foreign Language | English Language | Education and Training | History and Archeology | Philosophy and Theology | Sociology and Anthropology | Administrative | Geography</t>
+          <t>زبان خارجی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Speech Clarity | Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Speech Recognition | Inductive Reasoning | Near Vision | Deductive Reasoning | Problem Sensitivity | Selective Attention | Information Ordering</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mail | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Public Speaking | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Sitting | Frequency of Decision Making | Work With or Contribute to a Work Group or Team</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Art, Drama, and Music Teachers, Postsecondary | Communications Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Geography Teachers, Postsecondary | History Teachers, Postsecondary | Interpreters and Translators | Middle School Teachers, Except Special and Career/Technical Education | Philosophy and Religion Teachers, Postsecondary | Political Science Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | مترجمان شفاهی و کتبی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in scholarly journals, books, or electronic media. | Develop and maintain Web pages for teaching-related purposes. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in their field by reading current literature, talking with colleagues, and participating in professional organizations and activities. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Organize and direct study abroad programs. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as how to speak and write a foreign language and the cultural aspects of areas where a particular language is used. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding. | Write letters of recommendation for students.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | انجام پژوهش در یک حوزه دانشی مشخص و انتشار یافته‌ها در نشریات علمی، کتاب‌ها یا رسانه‌های الکترونیکی. | تدوین و نگهداری صفحات وب برای مقاصد آموزشی. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | به‌روز ماندن از تحولات حوزه تخصصی از راه مطالعه ادبیات روز، گفت‌وگو با همکاران و مشارکت در سازمان‌ها و فعالیت‌های تخصصی. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | سازماندهی و هدایت برنامه‌های تحصیل در خارج از کشور. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند شیوه گفتار و نگارش یک زبان خارجی و جنبه‌های فرهنگی مناطقی که آن زبان در آن‌ها به کار می‌رود. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید. | برای دانشجویان توصیه‌نامه بنویسید.</t>
         </is>
       </c>
     </row>
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>History Teachers, Postsecondary (مدرسان تاریخ، آموزش عالی)</t>
+          <t>مدرسان تاریخ، آموزش عالی (History Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adjunct History Instructor | Adjunct Instructor | Assistant Professor | Associate Professor | History Instructor | History Professor | History Teacher | Instructor | Lecturer | Professor</t>
+          <t>مدرس مدعو تاریخ | مربی مدعو | استادیار | دانشیار | مدرس تاریخ | استاد تاریخ | معلم تاریخ | مدرس | مدرس | استاد</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Collaborative editing software | Course management system software | DOC Cop | Database software | Desire2Learn LMS software | Email software | Geographic information system GIS software | Google Docs | Image scanning software | JavaScript | Learning management system LMS | Map building software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار پایگاه داده | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | نرم‌افزار اسکن تصویر | JavaScript | سیستم مدیریت یادگیری LMS | Map building software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Speaking | Reading Comprehension | Writing | Learning Strategies | Active Listening | Critical Thinking | Active Learning | Monitoring</t>
+          <t>سخن گفتن | درک مطلب | نگارش | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>History and Archeology | English Language | Education and Training | Law and Government | Geography | Sociology and Anthropology | Computers and Electronics | Philosophy and Theology | Communications and Media | Psychology</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | آموزش و پرورش | قانون و دولت | جغرافیا | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | فلسفه و الهیات | ارتباطات و رسانه | روان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Expression | Written Expression | Written Comprehension | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Near Vision | Speech Recognition | Problem Sensitivity | Category Flexibility | Information Ordering | Selective Attention | Originality | Fluency of Ideas</t>
+          <t>بیان شفاهی | بیان کتبی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Determine Tasks, Priorities and Goals | Freedom to Make Decisions | E-Mail | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Public Speaking | Contact With Others | Level of Competition | Frequency of Decision Making | Time Pressure | Written Letters and Memos | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Spend Time Sitting</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | سخنرانی عمومی | ارتباط با دیگران | سطح رقابت | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Art, Drama, and Music Teachers, Postsecondary | Communications Teachers, Postsecondary | Economics Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Foreign Language and Literature Teachers, Postsecondary | Geography Teachers, Postsecondary | Historians | Law Teachers, Postsecondary | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Philosophy and Religion Teachers, Postsecondary | Political Science Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Sociology Teachers, Postsecondary | Teaching Assistants, Postsecondary</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مدرسان ارتباطات، آموزش عالی | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان زبان و ادبیات خارجی، آموزش عالی | استادان جغرافیا، پس از متوسطه | مورخان | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Develop, maintain, and teach online courses. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as ancient history, postwar civilizations, and the history of third-world countries. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government, educational institutions, or industry. | Review books and journal articles for potential publication. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Teach community courses and speak to local groups and organizations. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | تدوین، نگهداری و تدریس دوره‌های برخط. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند تاریخ باستان، تمدن‌های پس از جنگ و تاریخ کشورهای جهان سوم. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | ارائه خدمات مشاوره تخصصی به دولت، نهادهای آموزشی یا صنعت. | کتاب‌ها و مقالات مجلات را برای انتشار احتمالی بررسی کنید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | تدریس دوره‌های عمومی و سخنرانی برای گروه‌ها و سازمان‌های محلی. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>

--- a/data_extactor/batch_10_fa/batch_0033_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0033_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | راهبردهای یادگیری | شنیدن فعال | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | راهبردهای یادگیری | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | مدیریت و امور اداری | ریاضیات | خدمات مشتریان و خدمات فردی | امور کارکنان و منابع انسانی | رایانه و الکترونیک | فلسفه و الهیات</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | مدیریت و اداره | ریاضیات | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان علوم ارتباطات دانشگاهی | مدیران آموزشی دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان روان‌شناسی دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی دانشگاهی | مربیان و مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدیران آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال</t>
+          <t>درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم رایانه دانشگاهی | مدیران آموزشی دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان حقوق دانشگاهی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، امور دفتری | کاردان‌ها و تکنسین‌های کتابداری | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی | دستیاران آموزشی دانشگاهی | مربیان و مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | تکنسین‌های کتابداری | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | حقوق و امور حکومتی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | روان‌شناسی | امور دفتری و اداری | امور کارکنان و منابع انسانی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | روان‌شناسی | اداری | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان علوم بازرگانی و مدیریت دانشگاهی | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم اقتصادی دانشگاهی | مدیران آموزشی دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی دانشگاهی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان حقوق دانشگاهی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان علوم سیاسی دانشگاهی | مدرسان روان‌شناسی دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | دبیران آموزش استثنایی دوره دوم متوسطه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دبیران آموزش استثنایی دوره دوم متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان علوم بازرگانی و مدیریت دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی دانشگاهی | مدرسان علوم اقتصادی دانشگاهی | مدیران آموزشی دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی دانشگاهی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | مدرسان تاریخ دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | وکلا و مشاوران حقوقی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | مدرسان فلسفه و الهیات دانشگاهی | مدرسان علوم سیاسی دانشگاهی | کارشناسان و پژوهشگران علوم سیاسی | مدرسان روان‌شناسی دانشگاهی | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | دستیاران آموزشی دانشگاهی</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | وکلا | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | دانشمندان و پژوهشگران علوم سیاسی | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | حقوق و امور حکومتی</t>
+          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | روانی و سیالی ایده‌ها | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | ابتکار</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم تربیتی دانشگاهی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان حقوق دانشگاهی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | مدرسان علوم سیاسی دانشگاهی | مدرسان روان‌شناسی دانشگاهی | مدرسان علوم اوقات فراغت و تربیت بدنی دانشگاهی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | جامعه‌شناسان | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی دانشگاهی</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | ابتکار | دید نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی و سیالی ایده‌ها | حساسیت به مسئله | دید دور | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | تشخیص رنگ‌ها | تجسم فضایی</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | اصالت | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | حساسیت به مسئله | بینایی دور | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان معماری دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | طراحان حرکات موزون و صحنه‌گردانان | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان تاریخ دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | رهبران ارکستر و آهنگسازان | مدرسان فلسفه و الهیات دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مربیان آموزش‌های آزاد و فوق‌برنامه | دستیاران آموزشی دانشگاهی | مربیان و مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | طراحان حرکت و کوروگراف‌ها | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | رهبران ارکستر، مدیران موسیقی و آهنگسازان | مدرسان فلسفه و الهیات در آموزش عالی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | خدمات مشتریان و خدمات فردی | فلسفه و الهیات | امور دفتری و اداری | تاریخ و باستان‌شناسی | مدیریت و امور اداری | هنرهای زیبا</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | فلسفه و الهیات | اداری | تاریخ و باستان‌شناسی | مدیریت و اداره | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات | حساسیت به مسئله | توجه انتخابی | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان علوم بازرگانی و مدیریت دانشگاهی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان حقوق دانشگاهی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات دانشگاهی | مدرسان علوم سیاسی دانشگاهی | مدرسان روان‌شناسی دانشگاهی | مدیران روابط عمومی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | دستیاران آموزشی دانشگاهی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | مدیران روابط عمومی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری | شنیدن فعال | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | روان‌شناسی | امور دفتری و اداری | هنرهای زیبا</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ارتباطات و رسانه | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | روان‌شناسی | اداری | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی و سیالی ایده‌ها | ابتکار | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان هنرهای تجسمی، نمایشی و موسیقی دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان علوم خانواده و مصرف‌کننده دانشگاهی | مدرسان زبان و ادبیات خارجی دانشگاهی | مدرسان تاریخ دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات دانشگاهی | مدرسان روان‌شناسی دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مربیان آموزش‌های آزاد و فوق‌برنامه | مدرسان جامعه‌شناسی دانشگاهی | دستیاران آموزشی دانشگاهی | مربیان و مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان‌های خارجی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | امور دفتری و اداری | جغرافیا</t>
+          <t>زبان خارجی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان هنرهای تجسمی، نمایشی و موسیقی دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان جغرافیا دانشگاهی | مدرسان تاریخ دانشگاهی | مترجمان همزمان و مترجمان متون | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات دانشگاهی | مدرسان علوم سیاسی دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مربیان آموزش‌های آزاد و فوق‌برنامه | مدرسان جامعه‌شناسی دانشگاهی | آموزگاران آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی دوره پیش‌دبستانی | مربیان و مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مترجمان کتبی و شفاهی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | نگارش | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | آموزش و پرورش | حقوق و امور حکومتی | جغرافیا | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | فلسفه و الهیات | ارتباطات و رسانه | روان‌شناسی</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | آموزش و پرورش | قانون و دولت | جغرافیا | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | فلسفه و الهیات | ارتباطات و رسانه | روان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | توجه انتخابی | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>بیان شفاهی | بیان کتبی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان هنرهای تجسمی، نمایشی و موسیقی دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان علوم اقتصادی دانشگاهی | مدرسان علوم تربیتی دانشگاهی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان زبان و ادبیات خارجی دانشگاهی | مدرسان جغرافیا دانشگاهی | تاریخ‌نگاران و پژوهشگران تاریخ | مدرسان حقوق دانشگاهی | مدرسان علم اطلاعات و دانش‌شناسی دانشگاهی | دبیران دوره اول متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات دانشگاهی | مدرسان علوم سیاسی دانشگاهی | دبیران دوره دوم متوسطه، به استثنای آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان جامعه‌شناسی دانشگاهی | دستیاران آموزشی دانشگاهی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مورخان | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
